--- a/dataset/01.w_Defects/free_nondynamic_allocated_memory.xlsx
+++ b/dataset/01.w_Defects/free_nondynamic_allocated_memory.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>char *free_nondynamic_allocated_memory_003_gbl_ptr; free_nondynamic_allocated_memory_struct_014 * free_nondynamic_allocated_memory_str ; char *free_nondynamic_allocated_memory_015_gbl_ptr; char *free_nondynamic_allocated_memory_016_gbl_ptr; char free_nondynamic_allocated_memory_016_gbl_var; extern volatile int vflag; void free_nondynamic_allocated_memory_016() { free_nondynamic_allocated_memory_016_gbl_var = 'A'; free_nondynamic_allocated_memory_016_func_001(); free_nondynamic_allocated_memory_016_func_002(); } void free_nondynamic_allocated_memory_016_func_001() { free_nondynamic_allocated_memory_016_gbl_ptr = "STRING"; } void free_nondynamic_allocated_memory_016_func_002() { if(free_nondynamic_allocated_memory_016_gbl_var =='A') free(free_nondynamic_allocated_memory_016_gbl_ptr);/*Tool should detect this line as error*/ /*ERROR:Free memory not allocated dynamically*/ }</t>
+          <t>char *free_nondynamic_allocated_memory_003_gbl_ptr; free_nondynamic_allocated_memory_struct_014 * free_nondynamic_allocated_memory_str ; char *free_nondynamic_allocated_memory_015_gbl_ptr; char *free_nondynamic_allocated_memory_016_gbl_ptr; char free_nondynamic_allocated_memory_016_gbl_var; extern volatile int vflag; void free_nondynamic_allocated_memory_016() { free_nondynamic_allocated_memory_016_gbl_var = 'A'; free_nondynamic_allocated_memory_016_func_001(); free_nondynamic_allocated_memory_016_func_002(); } void free_nondynamic_allocated_memory_016_func_002() { if(free_nondynamic_allocated_memory_016_gbl_var =='A') free(free_nondynamic_allocated_memory_016_gbl_ptr);/*Tool should detect this line as error*/ /*ERROR:Free memory not allocated dynamically*/ } void free_nondynamic_allocated_memory_016_func_001() { free_nondynamic_allocated_memory_016_gbl_ptr = "STRING"; }</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
